--- a/ДОЛГИ.xlsx
+++ b/ДОЛГИ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3972470C-1D1F-4E7D-A106-2B95B0A5B159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7935D5A4-42F2-4014-963B-E14376263225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="52">
   <si>
     <t>СБЕР</t>
   </si>
@@ -132,9 +132,6 @@
     <t>АРЕНДА</t>
   </si>
   <si>
-    <t>годовщина</t>
-  </si>
-  <si>
     <t>мама др</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>Оля др</t>
   </si>
   <si>
-    <t>Апрель</t>
-  </si>
-  <si>
     <t>Май</t>
   </si>
   <si>
@@ -187,6 +181,21 @@
   </si>
   <si>
     <t>25.05-31.05</t>
+  </si>
+  <si>
+    <t>копилка Оли</t>
+  </si>
+  <si>
+    <t>изменение долга за месяц (МАЙ)</t>
+  </si>
+  <si>
+    <t>05.05-10.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">занятие </t>
+  </si>
+  <si>
+    <t>06.05-10.05</t>
   </si>
 </sst>
 </file>
@@ -270,7 +279,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,6 +380,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -434,7 +455,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -533,11 +554,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Вывод" xfId="2" builtinId="21"/>
@@ -549,6 +583,9 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="solid">
@@ -558,16 +595,13 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="21" formatCode="dd/mmm"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="21" formatCode="dd/mmm"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="21" formatCode="dd/mmm"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="21" formatCode="dd/mmm"/>
@@ -586,13 +620,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2238854E-AC63-4FFE-8141-EE3370DA6D87}" name="Таблица26" displayName="Таблица26" ref="A1:D5" totalsRowCount="1">
-  <autoFilter ref="A1:D4" xr:uid="{2238854E-AC63-4FFE-8141-EE3370DA6D87}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2238854E-AC63-4FFE-8141-EE3370DA6D87}" name="Таблица26" displayName="Таблица26" ref="A1:D6" totalsRowCount="1">
+  <autoFilter ref="A1:D5" xr:uid="{2238854E-AC63-4FFE-8141-EE3370DA6D87}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D4DB3DB6-BC10-4B6D-9CE1-9FAA49126423}" name="min" totalsRowLabel="МАЙ" totalsRowDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E177E00A-82A3-4B30-8C98-796B530888B2}" name="Т-банк" dataDxfId="5" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D4DB3DB6-BC10-4B6D-9CE1-9FAA49126423}" name="min" totalsRowLabel="МАЙ" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E177E00A-82A3-4B30-8C98-796B530888B2}" name="Т-банк" dataDxfId="4" totalsRowDxfId="3"/>
     <tableColumn id="4" xr3:uid="{E3A4DFAB-AAA0-4818-A3C9-30FD63351198}" name="СБЕР"/>
-    <tableColumn id="7" xr3:uid="{C92C36D7-7E0C-4807-8339-861F21BFAF66}" name="TOTAL" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="0">
+    <tableColumn id="7" xr3:uid="{C92C36D7-7E0C-4807-8339-861F21BFAF66}" name="TOTAL" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="1">
       <calculatedColumnFormula>SUM(Таблица26[[#This Row],[Т-банк]:[СБЕР]])</calculatedColumnFormula>
       <totalsRowFormula>D2+D3</totalsRowFormula>
     </tableColumn>
@@ -607,7 +641,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{6291CC29-56AE-4E1B-8EA8-F4052A01E0E3}" name="ОБЯЗАТЕЛЬНЫЕ ТРАТЫ"/>
     <tableColumn id="2" xr3:uid="{259C8956-DF9A-469F-9E37-3B553F2F30D5}" name="СКОЛЬКО"/>
-    <tableColumn id="3" xr3:uid="{FDA3B0B2-B987-4248-8940-AA22E1B3B320}" name="ДАТА" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{FDA3B0B2-B987-4248-8940-AA22E1B3B320}" name="ДАТА" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{63BA4422-008C-4C9C-BB2F-8703204A700F}" name="ВСЕГО"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -626,10 +660,22 @@
 </table>
 </file>
 
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0602B9FB-A408-44A2-8366-9716243A5939}" name="Таблица142" displayName="Таблица142" ref="F1:H12" totalsRowShown="0">
+  <autoFilter ref="F1:H12" xr:uid="{0602B9FB-A408-44A2-8366-9716243A5939}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{CCFEF0C3-BB02-481E-9EC8-488C5841F5D4}" name="Доход"/>
+    <tableColumn id="2" xr3:uid="{81EA2C1D-2DA8-4EF5-A847-C62158DFD221}" name="сколько"/>
+    <tableColumn id="3" xr3:uid="{A49E4DBD-48A0-434F-A6F3-123D5CF65083}" name="когда"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Берлин">
   <a:themeElements>
-    <a:clrScheme name="Берлин">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -637,34 +683,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="9D360E"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="F09415"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C1B56B"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="4BAF73"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="5AA6C0"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="D17DF9"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="FA7E5C"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="FFAE3E"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="FCC77E"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Берлин">
@@ -889,9 +935,9 @@
     <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="5" width="11.5546875" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="34.5546875" customWidth="1"/>
-    <col min="8" max="8" width="33.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="7" max="7" width="38.5546875" customWidth="1"/>
+    <col min="8" max="8" width="37.33203125" customWidth="1"/>
     <col min="9" max="9" width="33" style="4" customWidth="1"/>
     <col min="10" max="10" width="35.21875" customWidth="1"/>
     <col min="11" max="11" width="34.109375" customWidth="1"/>
@@ -1245,8 +1291,8 @@
         <v>42712.77999999997</v>
       </c>
       <c r="I13" s="35">
-        <f>H13</f>
-        <v>42712.77999999997</v>
+        <f>H13+I18</f>
+        <v>26408.680000000051</v>
       </c>
       <c r="Q13" s="8"/>
     </row>
@@ -1278,7 +1324,7 @@
       <c r="O14" s="8"/>
       <c r="Q14" s="8"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>46141</v>
       </c>
@@ -1306,17 +1352,62 @@
       <c r="O15" s="8"/>
       <c r="U15" s="8"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
+    <row r="16" spans="1:21" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>1</v>
+      </c>
       <c r="I16"/>
       <c r="O16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="I17"/>
+    <row r="17" spans="1:30" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B17" s="5">
+        <v>495554.5</v>
+      </c>
+      <c r="C17" s="6">
+        <v>129750.93</v>
+      </c>
+      <c r="D17">
+        <v>76020.850000000006</v>
+      </c>
+      <c r="E17" s="59">
+        <v>-192330.64</v>
+      </c>
+      <c r="F17" s="63">
+        <v>-11689</v>
+      </c>
+      <c r="G17" s="64">
+        <f>SUM(B17:F17)</f>
+        <v>497306.6399999999</v>
+      </c>
+      <c r="H17" s="34">
+        <f>G17-F15</f>
+        <v>-24137.810000000056</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
       <c r="O17" s="8"/>
       <c r="Q17" s="28"/>
       <c r="R17" s="28"/>
@@ -1324,8 +1415,36 @@
       <c r="U17" s="29"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="I18"/>
+      <c r="A18" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B18" s="5">
+        <v>496334.5</v>
+      </c>
+      <c r="C18" s="5">
+        <v>129864.53</v>
+      </c>
+      <c r="D18" s="5">
+        <v>83419</v>
+      </c>
+      <c r="E18" s="67">
+        <v>-192409.68</v>
+      </c>
+      <c r="F18" s="68">
+        <v>-12068</v>
+      </c>
+      <c r="G18" s="64">
+        <f>SUM(B18:F18)</f>
+        <v>505140.35000000003</v>
+      </c>
+      <c r="H18" s="32">
+        <f>G18-G17</f>
+        <v>7833.7100000001374</v>
+      </c>
+      <c r="I18" s="31">
+        <f>H17+H18</f>
+        <v>-16304.099999999919</v>
+      </c>
       <c r="O18" s="8"/>
       <c r="P18" s="28"/>
       <c r="Q18" s="40"/>
@@ -1433,16 +1552,7 @@
     <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="I29"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="61"/>
-      <c r="R29" s="61"/>
-      <c r="S29" s="61"/>
+      <c r="J29" s="8"/>
       <c r="W29" s="13"/>
       <c r="X29" s="14"/>
       <c r="Y29" s="8"/>
@@ -1451,327 +1561,130 @@
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A30" s="60"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="60"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
-      <c r="S30" s="61"/>
+      <c r="A30" s="8"/>
+      <c r="I30"/>
+      <c r="J30" s="8"/>
       <c r="W30" s="13"/>
       <c r="X30" s="14"/>
       <c r="Y30" s="8"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A31" s="60"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="60"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
+      <c r="A31" s="8"/>
+      <c r="I31"/>
+      <c r="J31" s="8"/>
+      <c r="N31" s="60"/>
+      <c r="P31" s="60"/>
       <c r="W31" s="13"/>
       <c r="X31" s="14"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A32" s="60"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="61"/>
-      <c r="S32" s="61"/>
+      <c r="A32" s="8"/>
+      <c r="E32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="I32"/>
+      <c r="J32" s="8"/>
+      <c r="L32" s="60"/>
+      <c r="P32" s="60"/>
       <c r="Y32" s="8"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A33" s="60"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="61"/>
-      <c r="M33" s="61"/>
-      <c r="N33" s="61"/>
-      <c r="O33" s="61"/>
-      <c r="P33" s="62"/>
-      <c r="Q33" s="61"/>
-      <c r="R33" s="61"/>
-      <c r="S33" s="61"/>
+      <c r="A33" s="8"/>
+      <c r="C33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="I33"/>
+      <c r="J33" s="8"/>
+      <c r="P33" s="60"/>
       <c r="Z33" s="8"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A34" s="60"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="62"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="60"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
+      <c r="A34" s="8"/>
+      <c r="G34" s="60"/>
+      <c r="I34"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A35" s="60"/>
-      <c r="B35" s="61"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="60"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="61"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="61"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="61"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="61"/>
+      <c r="A35" s="8"/>
+      <c r="I35"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A36" s="60"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="60"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="61"/>
-      <c r="N36" s="61"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="61"/>
-      <c r="Q36" s="61"/>
-      <c r="R36" s="63"/>
-      <c r="S36" s="63"/>
+      <c r="A36" s="8"/>
+      <c r="I36"/>
+      <c r="J36" s="8"/>
+      <c r="L36" s="60"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A37" s="60"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="63"/>
-      <c r="S37" s="63"/>
+      <c r="A37" s="8"/>
+      <c r="C37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="8"/>
+      <c r="L37" s="60"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="61"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A38" s="60"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="60"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="61"/>
-      <c r="Q38" s="61"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
+      <c r="A38" s="8"/>
+      <c r="C38" s="60"/>
+      <c r="I38" s="61"/>
+      <c r="J38" s="8"/>
+      <c r="R38" s="61"/>
+      <c r="S38" s="61"/>
       <c r="U38" s="8"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A39" s="60"/>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="60"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="61"/>
-      <c r="N39" s="61"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="61"/>
-      <c r="Q39" s="61"/>
-      <c r="R39" s="63"/>
-      <c r="S39" s="63"/>
+      <c r="A39" s="8"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="8"/>
+      <c r="L39" s="60"/>
+      <c r="R39" s="61"/>
+      <c r="S39" s="61"/>
       <c r="T39" s="8"/>
       <c r="U39" s="37"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A40" s="60"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="63"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="61"/>
-      <c r="N40" s="61"/>
-      <c r="O40" s="61"/>
-      <c r="P40" s="61"/>
-      <c r="Q40" s="61"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="63"/>
+      <c r="A40" s="8"/>
+      <c r="C40" s="60"/>
+      <c r="I40" s="61"/>
+      <c r="J40" s="8"/>
+      <c r="L40" s="60"/>
+      <c r="R40" s="61"/>
+      <c r="S40" s="61"/>
       <c r="T40" s="37"/>
       <c r="U40" s="8"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A41" s="60"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="62"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="61"/>
-      <c r="N41" s="61"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="61"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="63"/>
-      <c r="S41" s="63"/>
+      <c r="A41" s="8"/>
+      <c r="C41" s="60"/>
+      <c r="I41" s="61"/>
+      <c r="J41" s="8"/>
+      <c r="R41" s="61"/>
+      <c r="S41" s="61"/>
       <c r="T41" s="8"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A42" s="60"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="63"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
-      <c r="N42" s="61"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="61"/>
-      <c r="Q42" s="61"/>
-      <c r="R42" s="63"/>
-      <c r="S42" s="63"/>
+      <c r="A42" s="8"/>
+      <c r="I42" s="61"/>
+      <c r="J42" s="8"/>
+      <c r="R42" s="61"/>
+      <c r="S42" s="61"/>
       <c r="U42" s="40"/>
       <c r="V42" s="8"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A43" s="60"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="63"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="61"/>
-      <c r="L43" s="61"/>
-      <c r="M43" s="61"/>
-      <c r="N43" s="61"/>
-      <c r="O43" s="61"/>
-      <c r="P43" s="61"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="63"/>
-      <c r="S43" s="63"/>
+      <c r="A43" s="8"/>
+      <c r="I43" s="61"/>
+      <c r="J43" s="8"/>
+      <c r="R43" s="61"/>
+      <c r="S43" s="61"/>
       <c r="V43" s="38"/>
       <c r="W43" s="39"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A44" s="60"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="A44" s="8"/>
+      <c r="I44" s="61"/>
+      <c r="J44" s="61"/>
       <c r="L44" s="38"/>
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
@@ -3901,7 +3814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271333B-52A5-44A7-B714-74741E8FFADD}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -3910,33 +3823,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
-        <v>43</v>
+      <c r="A1" s="62" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>48853.22</v>
       </c>
+      <c r="B2" s="65">
+        <v>8866</v>
+      </c>
+      <c r="C2" s="69">
+        <v>5032.29</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>A2/4</f>
         <v>12213.305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2216.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1258</v>
       </c>
     </row>
   </sheetData>
@@ -4003,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7E39A6-3A88-4B1C-9535-6FB8125A3282}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.109375" customWidth="1"/>
@@ -4016,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>0</v>
@@ -4030,11 +3969,11 @@
         <v>46159</v>
       </c>
       <c r="B2" s="29">
-        <v>79905</v>
+        <v>78144</v>
       </c>
       <c r="D2">
         <f>SUM(Таблица26[[#This Row],[Т-банк]:[СБЕР]])</f>
-        <v>79905</v>
+        <v>78144</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4064,13 +4003,26 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>43</v>
+      <c r="A5" s="8">
+        <v>46234</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="D5" s="46">
+      <c r="C5" s="30">
+        <v>113567.67999999999</v>
+      </c>
+      <c r="D5">
+        <f>SUM(Таблица26[[#This Row],[Т-банк]:[СБЕР]])</f>
+        <v>113567.67999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="D6" s="46">
         <f>D2+D3</f>
-        <v>162305.88</v>
+        <v>160544.88</v>
       </c>
     </row>
   </sheetData>
@@ -4109,9 +4061,6 @@
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="51"/>
       <c r="C2" s="53"/>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="51"/>
@@ -4119,7 +4068,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B4" s="52">
         <v>10000</v>
@@ -4132,7 +4081,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="52">
         <v>3500</v>
@@ -4142,17 +4091,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="55">
-        <v>12000</v>
-      </c>
+      <c r="B6" s="55"/>
       <c r="C6" s="53">
         <v>46143</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4167,24 +4111,24 @@
       </c>
       <c r="D7" s="29">
         <f>SUM(B6:B10)</f>
-        <v>84167</v>
+        <v>72167</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="51">
         <v>22000</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" s="29"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="52">
         <v>10000</v>
@@ -4195,7 +4139,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="52">
         <v>3500</v>
@@ -4207,7 +4151,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="52">
         <v>15000</v>
@@ -4216,7 +4160,7 @@
         <v>46182</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -4236,7 +4180,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="52">
         <v>3500</v>
@@ -4256,12 +4200,12 @@
         <v>46216</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="52">
         <v>3500</v>
@@ -4284,15 +4228,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DEDC91-58EF-418D-9066-1645D8AD2DEC}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="2" width="17.77734375" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -4302,52 +4249,97 @@
       <c r="C1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2">
         <v>22533</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1">
+        <v>22533</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="8">
+        <v>46150</v>
+      </c>
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="B3">
+      <c r="G3">
         <v>25000</v>
       </c>
-      <c r="C3" s="8">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H3" s="8">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46157</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="B4">
+      <c r="G4">
         <v>4700</v>
       </c>
-      <c r="C4" s="8">
-        <v>46145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H4" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46164</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="B5">
-        <v>65000</v>
-      </c>
-      <c r="C5" s="8">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>53000</v>
+      </c>
+      <c r="H5" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -4357,8 +4349,17 @@
       <c r="C6" s="8">
         <v>46157</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6">
+        <v>25000</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -4368,8 +4369,17 @@
       <c r="C7" s="8">
         <v>46162</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>18000</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -4379,32 +4389,63 @@
       <c r="C8" s="8">
         <v>46172</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C9" s="8"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1">
+        <v>29000</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>1000</v>
+      </c>
+      <c r="C9" s="8">
+        <v>46171</v>
+      </c>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" s="8"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" s="8"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="7">
         <f>SUM(B2:B8)</f>
-        <v>189233</v>
+        <v>97533</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="7">
+        <f>SUM(G2:G8)</f>
+        <v>177233</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>